--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1476,6 +1476,520 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128141758</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>547386</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6322716</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128141763</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>547550</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6322393</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128142664</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>547532</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6322396</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>blev troligen tagen av en duvhök. Inga avbitna fjädrar.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128142667</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57593</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>547532</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6322396</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>upphittade fjädrar vid resterna av en tjädertupp</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1990,6 +1990,867 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128293181</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>547494</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6322776</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128293205</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>547394</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6322764</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128293229</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>547484</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128293207</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>547260</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6322701</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128293222</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>547371</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6322586</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128293153</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>547760</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6322405</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128293162</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>547683</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6322521</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2361,7 +2361,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128293207</v>
+        <v>128293222</v>
       </c>
       <c r="B15" t="n">
         <v>57832</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547260</v>
+        <v>547371</v>
       </c>
       <c r="R15" t="n">
-        <v>6322701</v>
+        <v>6322586</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2484,7 +2484,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128293222</v>
+        <v>128293207</v>
       </c>
       <c r="B16" t="n">
         <v>57832</v>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547371</v>
+        <v>547260</v>
       </c>
       <c r="R16" t="n">
-        <v>6322586</v>
+        <v>6322701</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2851,6 +2851,1308 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128348197</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58042</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>547484</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128320890</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56554</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stora Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>547247</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6322734</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128320896</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56557</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stora Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>547247</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6322734</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128320990</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56559</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>547569</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6322310</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128320983</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56554</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>547569</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6322310</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128348205</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>547484</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128320974</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56540</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>547569</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6322310</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128320969</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56538</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>547569</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6322310</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128320900</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56559</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stora Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>547247</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6322734</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128320875</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56540</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stora Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>547247</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6322734</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -1481,7 +1481,7 @@
         <v>128141758</v>
       </c>
       <c r="B8" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128141763</v>
       </c>
       <c r="B9" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128142667</v>
       </c>
       <c r="B11" t="n">
-        <v>57593</v>
+        <v>57594</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>128293181</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>128293205</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>128293229</v>
       </c>
       <c r="B14" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>128293222</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>128293207</v>
       </c>
       <c r="B16" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128293153</v>
       </c>
       <c r="B17" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128293162</v>
       </c>
       <c r="B18" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>128348197</v>
       </c>
       <c r="B19" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>128348205</v>
       </c>
       <c r="B24" t="n">
-        <v>58349</v>
+        <v>58350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128320974</v>
+        <v>128320969</v>
       </c>
       <c r="B25" t="n">
-        <v>56540</v>
+        <v>56538</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128320969</v>
+        <v>128320974</v>
       </c>
       <c r="B26" t="n">
-        <v>56538</v>
+        <v>56540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -3623,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128320969</v>
+        <v>128320974</v>
       </c>
       <c r="B25" t="n">
-        <v>56538</v>
+        <v>56540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128320974</v>
+        <v>128320969</v>
       </c>
       <c r="B26" t="n">
-        <v>56540</v>
+        <v>56538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,7 +1481,7 @@
         <v>128141758</v>
       </c>
       <c r="B8" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128141763</v>
       </c>
       <c r="B9" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128142664</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128142667</v>
       </c>
       <c r="B11" t="n">
-        <v>57594</v>
+        <v>57606</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>128293181</v>
       </c>
       <c r="B12" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>128293205</v>
       </c>
       <c r="B13" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>128293229</v>
       </c>
       <c r="B14" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>128293222</v>
       </c>
       <c r="B15" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>128293207</v>
       </c>
       <c r="B16" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128293153</v>
       </c>
       <c r="B17" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128293162</v>
       </c>
       <c r="B18" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>128348197</v>
       </c>
       <c r="B19" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128320890</v>
+        <v>128320896</v>
       </c>
       <c r="B20" t="n">
-        <v>56554</v>
+        <v>56569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2983,26 +2983,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128320896</v>
+        <v>128320890</v>
       </c>
       <c r="B21" t="n">
-        <v>56557</v>
+        <v>56566</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,26 +3116,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3241,7 +3241,7 @@
         <v>128320990</v>
       </c>
       <c r="B22" t="n">
-        <v>56559</v>
+        <v>56571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>128320983</v>
       </c>
       <c r="B23" t="n">
-        <v>56554</v>
+        <v>56566</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>128348205</v>
       </c>
       <c r="B24" t="n">
-        <v>58350</v>
+        <v>58362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128320974</v>
       </c>
       <c r="B25" t="n">
-        <v>56540</v>
+        <v>56552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>128320969</v>
       </c>
       <c r="B26" t="n">
-        <v>56538</v>
+        <v>56550</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>128320900</v>
       </c>
       <c r="B27" t="n">
-        <v>56559</v>
+        <v>56571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>128320875</v>
       </c>
       <c r="B28" t="n">
-        <v>56540</v>
+        <v>56552</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4152,6 +4152,1602 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128495958</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>547248</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6322812</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128495915</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>547248</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6322812</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128496006</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>547473</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6322552</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128495925</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56566</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>547248</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6322812</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128495996</v>
+      </c>
+      <c r="B33" t="n">
+        <v>56550</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>547473</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6322552</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128495912</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56550</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>547248</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6322812</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128531054</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56566</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>547337</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6322798</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-01 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128531057</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56573</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>547337</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6322798</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-01 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128531047</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>547337</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6322798</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-01 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128610175</v>
+      </c>
+      <c r="B38" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-04 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128610181</v>
+      </c>
+      <c r="B39" t="n">
+        <v>56558</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-04 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128610186</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56569</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-04 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2361,7 +2361,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128293222</v>
+        <v>128293207</v>
       </c>
       <c r="B15" t="n">
         <v>57845</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547371</v>
+        <v>547260</v>
       </c>
       <c r="R15" t="n">
-        <v>6322586</v>
+        <v>6322701</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2484,7 +2484,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128293207</v>
+        <v>128293222</v>
       </c>
       <c r="B16" t="n">
         <v>57845</v>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547260</v>
+        <v>547371</v>
       </c>
       <c r="R16" t="n">
-        <v>6322701</v>
+        <v>6322586</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3623,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128320974</v>
+        <v>128320969</v>
       </c>
       <c r="B25" t="n">
-        <v>56552</v>
+        <v>56550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128320969</v>
+        <v>128320974</v>
       </c>
       <c r="B26" t="n">
-        <v>56550</v>
+        <v>56552</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5352,32 +5352,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128610175</v>
+        <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>56552</v>
+        <v>92084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>205998</v>
+        <v>6031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5387,34 +5387,24 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>registreringar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Store Flaten, Sm</t>
+          <t>Store Flaten, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547452</v>
+        <v>547439</v>
       </c>
       <c r="R38" t="n">
-        <v>6322404</v>
+        <v>6322473</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5438,27 +5428,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>wurb2024 ka-04 med Pettersson u384</t>
+          <t>nästan helt uppäten redan</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5467,6 +5457,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5485,10 +5476,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128610181</v>
+        <v>128626883</v>
       </c>
       <c r="B39" t="n">
-        <v>56558</v>
+        <v>57845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5496,55 +5487,50 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100086</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dammfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Myotis dasycneme</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(F.Boie, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Store Flaten, Sm</t>
+          <t>Store Flaten, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>547452</v>
+        <v>547446</v>
       </c>
       <c r="R39" t="n">
-        <v>6322404</v>
+        <v>6322522</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5571,27 +5557,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>wurb2024 ka-04 med Pettersson u384</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5618,69 +5599,64 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128610186</v>
+        <v>128626896</v>
       </c>
       <c r="B40" t="n">
-        <v>56569</v>
+        <v>57682</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100111</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>registreringar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Store Flaten, Sm</t>
+          <t>Stora Flaten, Grönskåra, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547452</v>
+        <v>547296</v>
       </c>
       <c r="R40" t="n">
-        <v>6322404</v>
+        <v>6322838</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5704,27 +5680,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>wurb2024 ka-04 med Pettersson u384</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5748,6 +5719,1318 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128626898</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Store Flaten, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>547471</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6322624</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128610175</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-04 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128627723</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56558</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>547248</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6322812</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128627241</v>
+      </c>
+      <c r="B44" t="n">
+        <v>96173</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Store Flaten, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>547437</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6322423</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>växer längs hela strandkanten</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128610181</v>
+      </c>
+      <c r="B45" t="n">
+        <v>56558</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-04 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128628222</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>547566</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6322282</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128610186</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56569</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6322404</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-04 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128628229</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56566</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>547566</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6322282</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128628224</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>547566</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6322282</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128628219</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56550</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>547566</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6322282</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2361,7 +2361,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128293207</v>
+        <v>128293222</v>
       </c>
       <c r="B15" t="n">
         <v>57845</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547260</v>
+        <v>547371</v>
       </c>
       <c r="R15" t="n">
-        <v>6322701</v>
+        <v>6322586</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2484,7 +2484,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128293222</v>
+        <v>128293207</v>
       </c>
       <c r="B16" t="n">
         <v>57845</v>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547371</v>
+        <v>547260</v>
       </c>
       <c r="R16" t="n">
-        <v>6322586</v>
+        <v>6322701</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -6369,37 +6369,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128628222</v>
+        <v>128610186</v>
       </c>
       <c r="B46" t="n">
-        <v>56552</v>
+        <v>56569</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6421,14 +6421,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stora Flatenvägen, Sm</t>
+          <t>Store Flaten, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547566</v>
+        <v>547452</v>
       </c>
       <c r="R46" t="n">
-        <v>6322282</v>
+        <v>6322404</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6455,17 +6455,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>wurb2024 AA-44 med Pettersson u384</t>
+          <t>wurb2024 ka-04 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6502,37 +6502,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128610186</v>
+        <v>128628222</v>
       </c>
       <c r="B47" t="n">
-        <v>56569</v>
+        <v>56552</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6554,14 +6554,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Store Flaten, Sm</t>
+          <t>Stora Flatenvägen, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547452</v>
+        <v>547566</v>
       </c>
       <c r="R47" t="n">
-        <v>6322404</v>
+        <v>6322282</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6588,17 +6588,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>wurb2024 ka-04 med Pettersson u384</t>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7032,6 +7032,1588 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128629766</v>
+      </c>
+      <c r="B51" t="n">
+        <v>56558</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6322412</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128629349</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>547578</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6322251</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128649231</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92085</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>547626</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6322276</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128629372</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>547512</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6322420</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128629342</v>
+      </c>
+      <c r="B55" t="n">
+        <v>56573</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>547578</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6322251</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128629347</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56566</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>547578</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6322251</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128629364</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56550</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>547512</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6322420</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128629309</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>547578</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6322251</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128629772</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6322412</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128629778</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>547452</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6322412</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128629307</v>
+      </c>
+      <c r="B61" t="n">
+        <v>56550</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>547578</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6322251</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128629374</v>
+      </c>
+      <c r="B62" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>547512</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6322420</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>wurb2024 ka-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -2361,7 +2361,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128293222</v>
+        <v>128293207</v>
       </c>
       <c r="B15" t="n">
         <v>57845</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547371</v>
+        <v>547260</v>
       </c>
       <c r="R15" t="n">
-        <v>6322586</v>
+        <v>6322701</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2484,7 +2484,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128293207</v>
+        <v>128293222</v>
       </c>
       <c r="B16" t="n">
         <v>57845</v>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547260</v>
+        <v>547371</v>
       </c>
       <c r="R16" t="n">
-        <v>6322701</v>
+        <v>6322586</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4158,7 +4158,7 @@
         <v>128495958</v>
       </c>
       <c r="B29" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>128495915</v>
       </c>
       <c r="B30" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>128496006</v>
       </c>
       <c r="B31" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>128495925</v>
       </c>
       <c r="B32" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>128495996</v>
       </c>
       <c r="B33" t="n">
-        <v>56550</v>
+        <v>56554</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128495912</v>
       </c>
       <c r="B34" t="n">
-        <v>56550</v>
+        <v>56554</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>128531054</v>
       </c>
       <c r="B35" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>128531057</v>
       </c>
       <c r="B36" t="n">
-        <v>56573</v>
+        <v>56577</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128531047</v>
       </c>
       <c r="B37" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92084</v>
+        <v>92090</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>128626883</v>
       </c>
       <c r="B39" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>128626896</v>
       </c>
       <c r="B40" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>128626898</v>
       </c>
       <c r="B41" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>128610175</v>
       </c>
       <c r="B42" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>128627723</v>
       </c>
       <c r="B43" t="n">
-        <v>56558</v>
+        <v>56562</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96173</v>
+        <v>96179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>128610181</v>
       </c>
       <c r="B45" t="n">
-        <v>56558</v>
+        <v>56562</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>128610186</v>
       </c>
       <c r="B46" t="n">
-        <v>56569</v>
+        <v>56573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>128628222</v>
       </c>
       <c r="B47" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>128628229</v>
       </c>
       <c r="B48" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>128628224</v>
       </c>
       <c r="B49" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128628219</v>
       </c>
       <c r="B50" t="n">
-        <v>56550</v>
+        <v>56554</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>128629766</v>
       </c>
       <c r="B51" t="n">
-        <v>56558</v>
+        <v>56562</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>128629349</v>
       </c>
       <c r="B52" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92085</v>
+        <v>92090</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>128629372</v>
       </c>
       <c r="B54" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>128629342</v>
       </c>
       <c r="B55" t="n">
-        <v>56573</v>
+        <v>56577</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>128629347</v>
       </c>
       <c r="B56" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>128629364</v>
       </c>
       <c r="B57" t="n">
-        <v>56550</v>
+        <v>56554</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>128629309</v>
       </c>
       <c r="B58" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>128629772</v>
       </c>
       <c r="B59" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>128629778</v>
       </c>
       <c r="B60" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>128629307</v>
       </c>
       <c r="B61" t="n">
-        <v>56550</v>
+        <v>56554</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>128629374</v>
       </c>
       <c r="B62" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -1481,7 +1481,7 @@
         <v>128141758</v>
       </c>
       <c r="B8" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128141763</v>
       </c>
       <c r="B9" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128142664</v>
       </c>
       <c r="B10" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128142667</v>
       </c>
       <c r="B11" t="n">
-        <v>57606</v>
+        <v>57610</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>128293181</v>
       </c>
       <c r="B12" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>128293205</v>
       </c>
       <c r="B13" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>128293229</v>
       </c>
       <c r="B14" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128293207</v>
+        <v>128293222</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547260</v>
+        <v>547371</v>
       </c>
       <c r="R15" t="n">
-        <v>6322701</v>
+        <v>6322586</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128293222</v>
+        <v>128293207</v>
       </c>
       <c r="B16" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547371</v>
+        <v>547260</v>
       </c>
       <c r="R16" t="n">
-        <v>6322586</v>
+        <v>6322701</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2610,7 +2610,7 @@
         <v>128293153</v>
       </c>
       <c r="B17" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128293162</v>
       </c>
       <c r="B18" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>128348197</v>
       </c>
       <c r="B19" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128320896</v>
+        <v>128320890</v>
       </c>
       <c r="B20" t="n">
-        <v>56569</v>
+        <v>56570</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2983,26 +2983,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128320890</v>
+        <v>128320896</v>
       </c>
       <c r="B21" t="n">
-        <v>56566</v>
+        <v>56573</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,26 +3116,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3241,7 +3241,7 @@
         <v>128320990</v>
       </c>
       <c r="B22" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>128320983</v>
       </c>
       <c r="B23" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>128348205</v>
       </c>
       <c r="B24" t="n">
-        <v>58362</v>
+        <v>58366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128320969</v>
       </c>
       <c r="B25" t="n">
-        <v>56550</v>
+        <v>56554</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>128320974</v>
       </c>
       <c r="B26" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>128320900</v>
       </c>
       <c r="B27" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>128320875</v>
       </c>
       <c r="B28" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8614,6 +8614,538 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128707285</v>
+      </c>
+      <c r="B63" t="n">
+        <v>56562</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>547451</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6322409</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128707289</v>
+      </c>
+      <c r="B64" t="n">
+        <v>56556</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>547451</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6322409</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128707452</v>
+      </c>
+      <c r="B65" t="n">
+        <v>56570</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>547451</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6322409</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128707318</v>
+      </c>
+      <c r="B66" t="n">
+        <v>56575</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Store Flaten, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>547451</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6322409</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-44 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -2361,7 +2361,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128293222</v>
+        <v>128293207</v>
       </c>
       <c r="B15" t="n">
         <v>57849</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547371</v>
+        <v>547260</v>
       </c>
       <c r="R15" t="n">
-        <v>6322586</v>
+        <v>6322701</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2484,7 +2484,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128293207</v>
+        <v>128293222</v>
       </c>
       <c r="B16" t="n">
         <v>57849</v>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547260</v>
+        <v>547371</v>
       </c>
       <c r="R16" t="n">
-        <v>6322701</v>
+        <v>6322586</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3623,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128320969</v>
+        <v>128320974</v>
       </c>
       <c r="B25" t="n">
-        <v>56554</v>
+        <v>56556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128320974</v>
+        <v>128320969</v>
       </c>
       <c r="B26" t="n">
-        <v>56556</v>
+        <v>56554</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2361,7 +2361,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128293207</v>
+        <v>128293222</v>
       </c>
       <c r="B15" t="n">
         <v>57849</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547260</v>
+        <v>547371</v>
       </c>
       <c r="R15" t="n">
-        <v>6322701</v>
+        <v>6322586</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2484,7 +2484,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128293222</v>
+        <v>128293207</v>
       </c>
       <c r="B16" t="n">
         <v>57849</v>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547371</v>
+        <v>547260</v>
       </c>
       <c r="R16" t="n">
-        <v>6322586</v>
+        <v>6322701</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3623,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128320974</v>
+        <v>128320969</v>
       </c>
       <c r="B25" t="n">
-        <v>56556</v>
+        <v>56554</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128320969</v>
+        <v>128320974</v>
       </c>
       <c r="B26" t="n">
-        <v>56554</v>
+        <v>56556</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -9146,6 +9146,137 @@
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128801352</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57702</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stora Flatenvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>547583</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6322234</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -2972,10 +2972,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128320890</v>
+        <v>128320896</v>
       </c>
       <c r="B20" t="n">
-        <v>56570</v>
+        <v>56573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2983,26 +2983,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128320896</v>
+        <v>128320890</v>
       </c>
       <c r="B21" t="n">
-        <v>56573</v>
+        <v>56570</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,26 +3116,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4158,7 +4158,7 @@
         <v>128495958</v>
       </c>
       <c r="B29" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>128495915</v>
       </c>
       <c r="B30" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>128496006</v>
       </c>
       <c r="B31" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>128495925</v>
       </c>
       <c r="B32" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>128495996</v>
       </c>
       <c r="B33" t="n">
-        <v>56554</v>
+        <v>56581</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128495912</v>
       </c>
       <c r="B34" t="n">
-        <v>56554</v>
+        <v>56581</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>128531054</v>
       </c>
       <c r="B35" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>128531057</v>
       </c>
       <c r="B36" t="n">
-        <v>56577</v>
+        <v>56604</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128531047</v>
       </c>
       <c r="B37" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>128626883</v>
       </c>
       <c r="B39" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>128626896</v>
       </c>
       <c r="B40" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>128626898</v>
       </c>
       <c r="B41" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>128610175</v>
       </c>
       <c r="B42" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>128627723</v>
       </c>
       <c r="B43" t="n">
-        <v>56562</v>
+        <v>56589</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>128610181</v>
       </c>
       <c r="B45" t="n">
-        <v>56562</v>
+        <v>56589</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>128610186</v>
       </c>
       <c r="B46" t="n">
-        <v>56573</v>
+        <v>56600</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>128628222</v>
       </c>
       <c r="B47" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>128628229</v>
       </c>
       <c r="B48" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>128628224</v>
       </c>
       <c r="B49" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128628219</v>
       </c>
       <c r="B50" t="n">
-        <v>56554</v>
+        <v>56581</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>128629766</v>
       </c>
       <c r="B51" t="n">
-        <v>56562</v>
+        <v>56589</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>128629349</v>
       </c>
       <c r="B52" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>128629372</v>
       </c>
       <c r="B54" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>128629342</v>
       </c>
       <c r="B55" t="n">
-        <v>56577</v>
+        <v>56604</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>128629347</v>
       </c>
       <c r="B56" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>128629364</v>
       </c>
       <c r="B57" t="n">
-        <v>56554</v>
+        <v>56581</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>128629309</v>
       </c>
       <c r="B58" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>128629772</v>
       </c>
       <c r="B59" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>128629778</v>
       </c>
       <c r="B60" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>128629307</v>
       </c>
       <c r="B61" t="n">
-        <v>56554</v>
+        <v>56581</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>128629374</v>
       </c>
       <c r="B62" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>128707285</v>
       </c>
       <c r="B63" t="n">
-        <v>56562</v>
+        <v>56589</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128707289</v>
       </c>
       <c r="B64" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>128707452</v>
       </c>
       <c r="B65" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>128707318</v>
       </c>
       <c r="B66" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>128801352</v>
       </c>
       <c r="B67" t="n">
-        <v>57702</v>
+        <v>57729</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -1995,7 +1995,7 @@
         <v>128293181</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>128293205</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>128293229</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128293222</v>
+        <v>128293207</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547371</v>
+        <v>547260</v>
       </c>
       <c r="R15" t="n">
-        <v>6322586</v>
+        <v>6322701</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128293207</v>
+        <v>128293222</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547260</v>
+        <v>547371</v>
       </c>
       <c r="R16" t="n">
-        <v>6322701</v>
+        <v>6322586</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2610,7 +2610,7 @@
         <v>128293153</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128293162</v>
       </c>
       <c r="B18" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>128348197</v>
       </c>
       <c r="B19" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128320896</v>
+        <v>128320890</v>
       </c>
       <c r="B20" t="n">
-        <v>56573</v>
+        <v>56597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2983,26 +2983,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128320890</v>
+        <v>128320896</v>
       </c>
       <c r="B21" t="n">
-        <v>56570</v>
+        <v>56600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,26 +3116,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3241,7 +3241,7 @@
         <v>128320990</v>
       </c>
       <c r="B22" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>128320983</v>
       </c>
       <c r="B23" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>128348205</v>
       </c>
       <c r="B24" t="n">
-        <v>58366</v>
+        <v>58393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128320969</v>
       </c>
       <c r="B25" t="n">
-        <v>56554</v>
+        <v>56581</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>128320974</v>
       </c>
       <c r="B26" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>128320900</v>
       </c>
       <c r="B27" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>128320875</v>
       </c>
       <c r="B28" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -2972,10 +2972,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128320890</v>
+        <v>128320896</v>
       </c>
       <c r="B20" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2983,26 +2983,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128320896</v>
+        <v>128320890</v>
       </c>
       <c r="B21" t="n">
-        <v>56600</v>
+        <v>56597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,26 +3116,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -3623,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128320969</v>
+        <v>128320974</v>
       </c>
       <c r="B25" t="n">
-        <v>56581</v>
+        <v>56583</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128320974</v>
+        <v>128320969</v>
       </c>
       <c r="B26" t="n">
-        <v>56583</v>
+        <v>56581</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4158,7 +4158,7 @@
         <v>128495958</v>
       </c>
       <c r="B29" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>128495915</v>
       </c>
       <c r="B30" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>128496006</v>
       </c>
       <c r="B31" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>128495925</v>
       </c>
       <c r="B32" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>128495996</v>
       </c>
       <c r="B33" t="n">
-        <v>56581</v>
+        <v>56584</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128495912</v>
       </c>
       <c r="B34" t="n">
-        <v>56581</v>
+        <v>56584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>128531054</v>
       </c>
       <c r="B35" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>128531057</v>
       </c>
       <c r="B36" t="n">
-        <v>56604</v>
+        <v>56607</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128531047</v>
       </c>
       <c r="B37" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>128626883</v>
       </c>
       <c r="B39" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>128626896</v>
       </c>
       <c r="B40" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>128626898</v>
       </c>
       <c r="B41" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>128610175</v>
       </c>
       <c r="B42" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>128627723</v>
       </c>
       <c r="B43" t="n">
-        <v>56589</v>
+        <v>56592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>128610181</v>
       </c>
       <c r="B45" t="n">
-        <v>56589</v>
+        <v>56592</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>128610186</v>
       </c>
       <c r="B46" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>128628222</v>
       </c>
       <c r="B47" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>128628229</v>
       </c>
       <c r="B48" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>128628224</v>
       </c>
       <c r="B49" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128628219</v>
       </c>
       <c r="B50" t="n">
-        <v>56581</v>
+        <v>56584</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>128629766</v>
       </c>
       <c r="B51" t="n">
-        <v>56589</v>
+        <v>56592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>128629349</v>
       </c>
       <c r="B52" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>128629372</v>
       </c>
       <c r="B54" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>128629342</v>
       </c>
       <c r="B55" t="n">
-        <v>56604</v>
+        <v>56607</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>128629347</v>
       </c>
       <c r="B56" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>128629364</v>
       </c>
       <c r="B57" t="n">
-        <v>56581</v>
+        <v>56584</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>128629309</v>
       </c>
       <c r="B58" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>128629772</v>
       </c>
       <c r="B59" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>128629778</v>
       </c>
       <c r="B60" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>128629307</v>
       </c>
       <c r="B61" t="n">
-        <v>56581</v>
+        <v>56584</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>128629374</v>
       </c>
       <c r="B62" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>128707285</v>
       </c>
       <c r="B63" t="n">
-        <v>56589</v>
+        <v>56592</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128707289</v>
       </c>
       <c r="B64" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>128707452</v>
       </c>
       <c r="B65" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>128707318</v>
       </c>
       <c r="B66" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>128801352</v>
       </c>
       <c r="B67" t="n">
-        <v>57729</v>
+        <v>57733</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -2856,7 +2856,7 @@
         <v>128348197</v>
       </c>
       <c r="B19" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128320896</v>
+        <v>128320890</v>
       </c>
       <c r="B20" t="n">
         <v>56600</v>
@@ -2983,26 +2983,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128320890</v>
+        <v>128320896</v>
       </c>
       <c r="B21" t="n">
-        <v>56597</v>
+        <v>56603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,26 +3116,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3241,7 +3241,7 @@
         <v>128320990</v>
       </c>
       <c r="B22" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>128320983</v>
       </c>
       <c r="B23" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>128348205</v>
       </c>
       <c r="B24" t="n">
-        <v>58393</v>
+        <v>58397</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128320974</v>
+        <v>128320969</v>
       </c>
       <c r="B25" t="n">
-        <v>56583</v>
+        <v>56584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128320969</v>
+        <v>128320974</v>
       </c>
       <c r="B26" t="n">
-        <v>56581</v>
+        <v>56586</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3892,7 +3892,7 @@
         <v>128320900</v>
       </c>
       <c r="B27" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>128320875</v>
       </c>
       <c r="B28" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -4158,7 +4158,7 @@
         <v>128495958</v>
       </c>
       <c r="B29" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>128495915</v>
       </c>
       <c r="B30" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>128496006</v>
       </c>
       <c r="B31" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>128495925</v>
       </c>
       <c r="B32" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>128495996</v>
       </c>
       <c r="B33" t="n">
-        <v>56584</v>
+        <v>56587</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128495912</v>
       </c>
       <c r="B34" t="n">
-        <v>56584</v>
+        <v>56587</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>128531054</v>
       </c>
       <c r="B35" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>128531057</v>
       </c>
       <c r="B36" t="n">
-        <v>56607</v>
+        <v>56610</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128531047</v>
       </c>
       <c r="B37" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>128626883</v>
       </c>
       <c r="B39" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>128626896</v>
       </c>
       <c r="B40" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>128626898</v>
       </c>
       <c r="B41" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>128610175</v>
       </c>
       <c r="B42" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>128627723</v>
       </c>
       <c r="B43" t="n">
-        <v>56592</v>
+        <v>56595</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>128610181</v>
       </c>
       <c r="B45" t="n">
-        <v>56592</v>
+        <v>56595</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>128610186</v>
       </c>
       <c r="B46" t="n">
-        <v>56603</v>
+        <v>56606</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>128628222</v>
       </c>
       <c r="B47" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>128628229</v>
       </c>
       <c r="B48" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>128628224</v>
       </c>
       <c r="B49" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128628219</v>
       </c>
       <c r="B50" t="n">
-        <v>56584</v>
+        <v>56587</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>128629766</v>
       </c>
       <c r="B51" t="n">
-        <v>56592</v>
+        <v>56595</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>128629349</v>
       </c>
       <c r="B52" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>128629372</v>
       </c>
       <c r="B54" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>128629342</v>
       </c>
       <c r="B55" t="n">
-        <v>56607</v>
+        <v>56610</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>128629347</v>
       </c>
       <c r="B56" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>128629364</v>
       </c>
       <c r="B57" t="n">
-        <v>56584</v>
+        <v>56587</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>128629309</v>
       </c>
       <c r="B58" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>128629772</v>
       </c>
       <c r="B59" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>128629778</v>
       </c>
       <c r="B60" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>128629307</v>
       </c>
       <c r="B61" t="n">
-        <v>56584</v>
+        <v>56587</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>128629374</v>
       </c>
       <c r="B62" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>128707285</v>
       </c>
       <c r="B63" t="n">
-        <v>56592</v>
+        <v>56595</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128707289</v>
       </c>
       <c r="B64" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>128707452</v>
       </c>
       <c r="B65" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>128707318</v>
       </c>
       <c r="B66" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>128801352</v>
       </c>
       <c r="B67" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -5355,7 +5355,7 @@
         <v>128621420</v>
       </c>
       <c r="B38" t="n">
-        <v>92153</v>
+        <v>92161</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>128627241</v>
       </c>
       <c r="B44" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92153</v>
+        <v>92161</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -7037,7 +7037,7 @@
         <v>128629766</v>
       </c>
       <c r="B51" t="n">
-        <v>56595</v>
+        <v>56597</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>128629349</v>
       </c>
       <c r="B52" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128649231</v>
       </c>
       <c r="B53" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>128629372</v>
       </c>
       <c r="B54" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>128629342</v>
       </c>
       <c r="B55" t="n">
-        <v>56610</v>
+        <v>56612</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>128629347</v>
       </c>
       <c r="B56" t="n">
-        <v>56603</v>
+        <v>56605</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>128629364</v>
       </c>
       <c r="B57" t="n">
-        <v>56587</v>
+        <v>56589</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>128629309</v>
       </c>
       <c r="B58" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>128629772</v>
       </c>
       <c r="B59" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>128629778</v>
       </c>
       <c r="B60" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>128629307</v>
       </c>
       <c r="B61" t="n">
-        <v>56587</v>
+        <v>56589</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>128629374</v>
       </c>
       <c r="B62" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>128707285</v>
       </c>
       <c r="B63" t="n">
-        <v>56595</v>
+        <v>56597</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128707289</v>
       </c>
       <c r="B64" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>128707452</v>
       </c>
       <c r="B65" t="n">
-        <v>56603</v>
+        <v>56605</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>128707318</v>
       </c>
       <c r="B66" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>128801352</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -8619,7 +8619,7 @@
         <v>128707285</v>
       </c>
       <c r="B63" t="n">
-        <v>56597</v>
+        <v>56599</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128707289</v>
       </c>
       <c r="B64" t="n">
-        <v>56591</v>
+        <v>56593</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>128707452</v>
       </c>
       <c r="B65" t="n">
-        <v>56605</v>
+        <v>56607</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>128707318</v>
       </c>
       <c r="B66" t="n">
-        <v>56610</v>
+        <v>56612</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>128801352</v>
       </c>
       <c r="B67" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9277,6 +9277,244 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129396098</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92193</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Store Flaten, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>547280</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6322673</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129396099</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92193</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Store Flaten, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>547269</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6322689</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9515,6 +9515,137 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129416631</v>
+      </c>
+      <c r="B70" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>547354</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6322721</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9646,6 +9646,268 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129545905</v>
+      </c>
+      <c r="B71" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>547707</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6322242</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129545906</v>
+      </c>
+      <c r="B72" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>547727</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6322462</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>129416631</v>
       </c>
       <c r="B70" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>129545905</v>
       </c>
       <c r="B71" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>129545906</v>
       </c>
       <c r="B72" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>129416631</v>
       </c>
       <c r="B70" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>129545905</v>
       </c>
       <c r="B71" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>129545906</v>
       </c>
       <c r="B72" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>129416631</v>
       </c>
       <c r="B70" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>129545905</v>
       </c>
       <c r="B71" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>129545906</v>
       </c>
       <c r="B72" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
         <v>129396098</v>
       </c>
       <c r="B68" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129396099</v>
       </c>
       <c r="B69" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41226-2025 artfynd.xlsx
+++ b/artfynd/A 41226-2025 artfynd.xlsx
@@ -9651,7 +9651,7 @@
         <v>129545905</v>
       </c>
       <c r="B71" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>129545906</v>
       </c>
       <c r="B72" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
